--- a/public/plantilla-ficha-vias.xlsx
+++ b/public/plantilla-ficha-vias.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="170" formatCode="&quot;$ &quot;#,##0.00"/>
     <numFmt numFmtId="171" formatCode="&quot;$ &quot;#,##0"/>
   </numFmts>
-  <fonts count="170">
+  <fonts count="173">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -1242,6 +1242,20 @@
       <name val="Calibri"/>
       <family val="2"/>
       <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF0000FF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -6498,7 +6512,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1387">
+  <cellXfs count="1394">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -9909,6 +9923,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="398" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="51" fillId="3" borderId="392" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="170" fillId="76" borderId="393" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="171" fillId="76" borderId="393" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="170" fillId="77" borderId="392" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="171" fillId="77" borderId="392" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="170" fillId="76" borderId="392" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="171" fillId="76" borderId="392" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="172" fillId="0" borderId="392" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -10460,13 +10495,13 @@
       <c r="C14" s="641" t="n"/>
       <c r="E14" s="1381" t="n"/>
     </row>
-    <row r="15">
-      <c r="A15" s="585" t="inlineStr">
+    <row r="15" ht="16" customHeight="1" s="614">
+      <c r="A15" s="1387" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="B15" s="587" t="inlineStr">
+      <c r="B15" s="1388" t="inlineStr">
         <is>
           <t>Rural</t>
         </is>
@@ -10488,13 +10523,13 @@
       <c r="C16" s="641" t="n"/>
       <c r="E16" s="1381" t="n"/>
     </row>
-    <row r="17">
-      <c r="A17" s="585" t="inlineStr">
+    <row r="17" ht="16" customHeight="1" s="614">
+      <c r="A17" s="1387" t="inlineStr">
         <is>
           <t>Longitud total (km)</t>
         </is>
       </c>
-      <c r="B17" s="584" t="n">
+      <c r="B17" s="1388" t="n">
         <v>225</v>
       </c>
       <c r="C17" s="640" t="n"/>
@@ -10512,13 +10547,13 @@
       <c r="C18" s="641" t="n"/>
       <c r="E18" s="1381" t="n"/>
     </row>
-    <row r="19">
-      <c r="A19" s="585" t="inlineStr">
+    <row r="19" ht="16" customHeight="1" s="614">
+      <c r="A19" s="1387" t="inlineStr">
         <is>
           <t>Velocidad de diseño (km/h)</t>
         </is>
       </c>
-      <c r="B19" s="584" t="n">
+      <c r="B19" s="1388" t="n">
         <v>65</v>
       </c>
       <c r="C19" s="640" t="n"/>
@@ -10536,13 +10571,13 @@
       <c r="C20" s="641" t="n"/>
       <c r="E20" s="1381" t="n"/>
     </row>
-    <row r="21">
-      <c r="A21" s="585" t="inlineStr">
+    <row r="21" ht="16" customHeight="1" s="614">
+      <c r="A21" s="1387" t="inlineStr">
         <is>
           <t>Ancho de carril (m)</t>
         </is>
       </c>
-      <c r="B21" s="584" t="n">
+      <c r="B21" s="1388" t="n">
         <v>3.65</v>
       </c>
       <c r="C21" s="640" t="n"/>
@@ -10560,13 +10595,13 @@
       <c r="C22" s="641" t="n"/>
       <c r="E22" s="1381" t="n"/>
     </row>
-    <row r="23">
-      <c r="A23" s="585" t="inlineStr">
+    <row r="23" ht="16" customHeight="1" s="614">
+      <c r="A23" s="1387" t="inlineStr">
         <is>
           <t>Pendiente máxima (%)</t>
         </is>
       </c>
-      <c r="B23" s="584" t="n">
+      <c r="B23" s="1388" t="n">
         <v>4</v>
       </c>
       <c r="C23" s="640" t="n"/>
@@ -10586,13 +10621,13 @@
       <c r="C24" s="641" t="n"/>
       <c r="E24" s="1381" t="n"/>
     </row>
-    <row r="25">
-      <c r="A25" s="585" t="inlineStr">
+    <row r="25" ht="16" customHeight="1" s="614">
+      <c r="A25" s="1387" t="inlineStr">
         <is>
           <t>CBR de diseño (%)</t>
         </is>
       </c>
-      <c r="B25" s="584" t="n">
+      <c r="B25" s="1388" t="n">
         <v>3</v>
       </c>
       <c r="C25" s="640" t="n"/>
@@ -10610,13 +10645,13 @@
       <c r="C26" s="641" t="n"/>
       <c r="E26" s="1381" t="n"/>
     </row>
-    <row r="27">
-      <c r="A27" s="585" t="inlineStr">
+    <row r="27" ht="16" customHeight="1" s="614">
+      <c r="A27" s="1387" t="inlineStr">
         <is>
           <t>Base granular (cm)</t>
         </is>
       </c>
-      <c r="B27" s="584" t="n">
+      <c r="B27" s="1388" t="n">
         <v>15</v>
       </c>
       <c r="C27" s="640" t="n"/>
@@ -10647,26 +10682,26 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="580" t="inlineStr">
+    <row r="31" ht="16" customHeight="1" s="614">
+      <c r="A31" s="1389" t="inlineStr">
         <is>
           <t>Administración (A)</t>
         </is>
       </c>
-      <c r="B31" s="1382" t="n">
+      <c r="B31" s="1390" t="n">
         <v>0.1</v>
       </c>
       <c r="C31" s="577" t="n"/>
       <c r="D31" s="577" t="n"/>
       <c r="E31" s="577" t="n"/>
     </row>
-    <row r="32">
-      <c r="A32" s="576" t="inlineStr">
+    <row r="32" ht="16" customHeight="1" s="614">
+      <c r="A32" s="1391" t="inlineStr">
         <is>
           <t>Imprevistos (I)</t>
         </is>
       </c>
-      <c r="B32" s="1383" t="n">
+      <c r="B32" s="1392" t="n">
         <v>0.04</v>
       </c>
       <c r="C32" s="574" t="n"/>
@@ -10679,20 +10714,20 @@
           <t>Utilidad (U)</t>
         </is>
       </c>
-      <c r="B33" s="1382" t="n">
+      <c r="B33" s="1390" t="n">
         <v>0.12</v>
       </c>
       <c r="C33" s="577" t="n"/>
       <c r="D33" s="577" t="n"/>
       <c r="E33" s="577" t="n"/>
     </row>
-    <row r="34">
-      <c r="A34" s="576" t="inlineStr">
+    <row r="34" ht="16" customHeight="1" s="614">
+      <c r="A34" s="1391" t="inlineStr">
         <is>
           <t>IVA sobre Utilidad</t>
         </is>
       </c>
-      <c r="B34" s="1383" t="n">
+      <c r="B34" s="1392" t="n">
         <v>0.19</v>
       </c>
       <c r="C34" s="574" t="n"/>
@@ -10706,8 +10741,8 @@
       <c r="D35" s="1384" t="n"/>
       <c r="E35" s="1385" t="n"/>
     </row>
-    <row r="36" ht="15" customFormat="1" customHeight="1" s="643">
-      <c r="A36" s="573" t="inlineStr">
+    <row r="36" ht="16" customFormat="1" customHeight="1" s="643">
+      <c r="A36" s="1393" t="inlineStr">
         <is>
           <t>AIU TOTAL (A+I+U)</t>
         </is>
